--- a/car_log_template.xlsx
+++ b/car_log_template.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <x:si>
     <x:t>【차량번호: 721라 9540 / 차량  : 스타리아】</x:t>
   </x:si>
@@ -56,6 +56,57 @@
   </x:si>
   <x:si>
     <x:t>운행 후  (누적Km)</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve"> </x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="경기천년제목V Bold"/>
+            <x:sz val="15"/>
+            <x:color rgb="ff000000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="경기천년제목V Bold"/>
+            <x:sz val="15"/>
+            <x:color rgb="ff000000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>07월 차량운행일지</x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="경기천년제목V Bold"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff000000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="경기천년제목V Bold"/>
+            <x:sz val="11"/>
+            <x:color rgb="ff000000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t xml:space="preserve"> </x:t>
+    </x:r>
   </x:si>
   <x:si>
     <x:t>도착시간</x:t>
@@ -117,7 +168,7 @@
     <x:numFmt numFmtId="166" formatCode="00&quot;.&quot;00&quot;.&quot;00"/>
     <x:numFmt numFmtId="167" formatCode="00&quot;:&quot;00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -168,12 +219,12 @@
       <x:name val="경기천년바탕 Bold"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
+      <x:b val="1"/>
     </x:font>
     <x:font>
       <x:name val="경기천년바탕 Bold"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
-      <x:b val="1"/>
     </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
@@ -191,6 +242,26 @@
         <x:font>
           <x:name val="경기천년제목V Bold"/>
           <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="경기천년제목V Bold"/>
+          <x:sz val="15"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="경기천년제목V Bold"/>
+          <x:sz val="15"/>
           <x:color rgb="ff000000"/>
         </x:font>
       </mc:Fallback>
@@ -238,7 +309,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="13">
+  <x:borders count="7">
     <x:border>
       <x:left>
         <x:color rgb="ff000000"/>
@@ -334,90 +405,6 @@
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right>
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom>
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left>
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom>
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right>
-        <x:color auto="1"/>
-      </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom>
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left>
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom>
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right>
-        <x:color auto="1"/>
-      </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left>
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
@@ -430,7 +417,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -484,6 +471,19 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
@@ -526,27 +526,53 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -591,40 +617,40 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+        <x:xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <x:protection locked="0"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
           <x:alignment horizontal="center" vertical="center"/>
           <x:protection locked="0"/>
         </x:xf>
@@ -665,7 +691,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -700,6 +726,32 @@
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
@@ -777,6 +829,32 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
@@ -788,85 +866,15 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-          <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -1211,68 +1219,70 @@
     <x:row r="1" spans="1:31" ht="21.75" customHeight="1">
       <x:c r="A1" s="6"/>
       <x:c r="B1" s="2"/>
-      <x:c r="C1" s="19"/>
-      <x:c r="D1" s="19"/>
-      <x:c r="E1" s="19"/>
-      <x:c r="F1" s="19"/>
-      <x:c r="G1" s="19"/>
-      <x:c r="H1" s="19"/>
-      <x:c r="I1" s="19"/>
-      <x:c r="J1" s="19"/>
-      <x:c r="N1" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="O1" s="21"/>
-      <x:c r="P1" s="20"/>
-      <x:c r="Q1" s="20"/>
-      <x:c r="R1" s="20"/>
-      <x:c r="S1" s="20"/>
-      <x:c r="T1" s="20" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="U1" s="20"/>
-      <x:c r="V1" s="20"/>
-      <x:c r="W1" s="20"/>
-      <x:c r="X1" s="20"/>
-      <x:c r="Y1" s="20"/>
-      <x:c r="Z1" s="20" t="s">
+      <x:c r="C1" s="22" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="N1" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="O1" s="24"/>
+      <x:c r="P1" s="23"/>
+      <x:c r="Q1" s="23"/>
+      <x:c r="R1" s="23"/>
+      <x:c r="S1" s="23"/>
+      <x:c r="T1" s="23" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="U1" s="23"/>
+      <x:c r="V1" s="23"/>
+      <x:c r="W1" s="23"/>
+      <x:c r="X1" s="23"/>
+      <x:c r="Y1" s="23"/>
+      <x:c r="Z1" s="23" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AA1" s="20"/>
-      <x:c r="AB1" s="20"/>
-      <x:c r="AC1" s="20"/>
-      <x:c r="AD1" s="20"/>
-      <x:c r="AE1" s="20"/>
+      <x:c r="AA1" s="23"/>
+      <x:c r="AB1" s="23"/>
+      <x:c r="AC1" s="23"/>
+      <x:c r="AD1" s="23"/>
+      <x:c r="AE1" s="23"/>
     </x:row>
     <x:row r="2" spans="1:31" ht="4.5" customHeight="1">
       <x:c r="A2" s="6"/>
       <x:c r="B2" s="2"/>
-      <x:c r="C2" s="19"/>
-      <x:c r="D2" s="19"/>
-      <x:c r="E2" s="19"/>
-      <x:c r="F2" s="19"/>
-      <x:c r="G2" s="19"/>
-      <x:c r="H2" s="19"/>
-      <x:c r="I2" s="19"/>
-      <x:c r="J2" s="19"/>
-      <x:c r="N2" s="22"/>
-      <x:c r="O2" s="22"/>
-      <x:c r="P2" s="22"/>
-      <x:c r="Q2" s="22"/>
-      <x:c r="R2" s="23"/>
-      <x:c r="S2" s="23"/>
-      <x:c r="T2" s="23"/>
-      <x:c r="U2" s="23"/>
-      <x:c r="V2" s="23"/>
-      <x:c r="W2" s="23"/>
-      <x:c r="X2" s="23"/>
-      <x:c r="Y2" s="23"/>
-      <x:c r="Z2" s="23"/>
-      <x:c r="AA2" s="23"/>
-      <x:c r="AB2" s="23"/>
-      <x:c r="AC2" s="23"/>
-      <x:c r="AD2" s="23"/>
-      <x:c r="AE2" s="23"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="N2" s="25"/>
+      <x:c r="O2" s="25"/>
+      <x:c r="P2" s="25"/>
+      <x:c r="Q2" s="25"/>
+      <x:c r="R2" s="26"/>
+      <x:c r="S2" s="26"/>
+      <x:c r="T2" s="26"/>
+      <x:c r="U2" s="26"/>
+      <x:c r="V2" s="26"/>
+      <x:c r="W2" s="26"/>
+      <x:c r="X2" s="26"/>
+      <x:c r="Y2" s="26"/>
+      <x:c r="Z2" s="26"/>
+      <x:c r="AA2" s="26"/>
+      <x:c r="AB2" s="26"/>
+      <x:c r="AC2" s="26"/>
+      <x:c r="AD2" s="26"/>
+      <x:c r="AE2" s="26"/>
     </x:row>
     <x:row r="3" spans="1:31" ht="39.75" customHeight="1">
       <x:c r="A3" s="2"/>
@@ -1285,379 +1295,379 @@
       <x:c r="H3" s="2"/>
       <x:c r="I3" s="2"/>
       <x:c r="J3" s="2"/>
-      <x:c r="N3" s="22"/>
-      <x:c r="O3" s="22"/>
-      <x:c r="P3" s="22"/>
-      <x:c r="Q3" s="22"/>
-      <x:c r="R3" s="22"/>
-      <x:c r="S3" s="22"/>
-      <x:c r="T3" s="22"/>
-      <x:c r="U3" s="22"/>
-      <x:c r="V3" s="23"/>
-      <x:c r="W3" s="23"/>
-      <x:c r="X3" s="23"/>
-      <x:c r="Y3" s="23"/>
-      <x:c r="Z3" s="23"/>
-      <x:c r="AA3" s="23"/>
-      <x:c r="AB3" s="23"/>
-      <x:c r="AC3" s="23"/>
-      <x:c r="AD3" s="23"/>
-      <x:c r="AE3" s="23"/>
+      <x:c r="N3" s="25"/>
+      <x:c r="O3" s="25"/>
+      <x:c r="P3" s="25"/>
+      <x:c r="Q3" s="25"/>
+      <x:c r="R3" s="25"/>
+      <x:c r="S3" s="25"/>
+      <x:c r="T3" s="25"/>
+      <x:c r="U3" s="25"/>
+      <x:c r="V3" s="26"/>
+      <x:c r="W3" s="26"/>
+      <x:c r="X3" s="26"/>
+      <x:c r="Y3" s="26"/>
+      <x:c r="Z3" s="26"/>
+      <x:c r="AA3" s="26"/>
+      <x:c r="AB3" s="26"/>
+      <x:c r="AC3" s="26"/>
+      <x:c r="AD3" s="26"/>
+      <x:c r="AE3" s="26"/>
     </x:row>
     <x:row r="4" spans="1:7" ht="20.25" customHeight="1">
-      <x:c r="A4" s="24" t="s">
+      <x:c r="A4" s="27" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B4" s="25"/>
-      <x:c r="C4" s="25"/>
-      <x:c r="D4" s="25"/>
-      <x:c r="E4" s="25"/>
-      <x:c r="F4" s="25"/>
-      <x:c r="G4" s="25"/>
+      <x:c r="B4" s="28"/>
+      <x:c r="C4" s="28"/>
+      <x:c r="D4" s="28"/>
+      <x:c r="E4" s="28"/>
+      <x:c r="F4" s="28"/>
+      <x:c r="G4" s="28"/>
     </x:row>
     <x:row r="5" spans="1:32" ht="34" customHeight="1">
-      <x:c r="A5" s="26" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B5" s="27"/>
+      <x:c r="A5" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="30"/>
       <x:c r="C5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="J5" s="44" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K5" s="45"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J5" s="31" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K5" s="32"/>
       <x:c r="L5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N5" s="28" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N5" s="33" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O5" s="34"/>
+      <x:c r="P5" s="35"/>
+      <x:c r="Q5" s="34"/>
+      <x:c r="R5" s="34"/>
+      <x:c r="S5" s="35"/>
+      <x:c r="T5" s="34"/>
+      <x:c r="U5" s="34"/>
+      <x:c r="V5" s="34"/>
+      <x:c r="W5" s="34"/>
+      <x:c r="X5" s="34"/>
+      <x:c r="Y5" s="34"/>
+      <x:c r="Z5" s="33" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="O5" s="29"/>
-      <x:c r="P5" s="30"/>
-      <x:c r="Q5" s="29"/>
-      <x:c r="R5" s="29"/>
-      <x:c r="S5" s="30"/>
-      <x:c r="T5" s="29"/>
-      <x:c r="U5" s="29"/>
-      <x:c r="V5" s="29"/>
-      <x:c r="W5" s="29"/>
-      <x:c r="X5" s="29"/>
-      <x:c r="Y5" s="29"/>
-      <x:c r="Z5" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="AA5" s="29"/>
-      <x:c r="AB5" s="29"/>
-      <x:c r="AC5" s="29"/>
-      <x:c r="AD5" s="29"/>
-      <x:c r="AE5" s="31"/>
-      <x:c r="AF5" s="10"/>
+      <x:c r="AA5" s="34"/>
+      <x:c r="AB5" s="34"/>
+      <x:c r="AC5" s="34"/>
+      <x:c r="AD5" s="34"/>
+      <x:c r="AE5" s="36"/>
+      <x:c r="AF5" s="11"/>
     </x:row>
     <x:row r="6" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A6" s="32">
+      <x:c r="A6" s="37">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="33"/>
-      <x:c r="C6" s="16"/>
-      <x:c r="D6" s="17"/>
-      <x:c r="E6" s="17"/>
-      <x:c r="F6" s="11"/>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="B6" s="38"/>
+      <x:c r="C6" s="19"/>
+      <x:c r="D6" s="20"/>
+      <x:c r="E6" s="20"/>
+      <x:c r="F6" s="13"/>
+      <x:c r="G6" s="14" t="str">
         <x:f>IF(OR(LEN(F6)=0,LEN(H6)=0),"",H6-F6)</x:f>
         <x:v/>
       </x:c>
-      <x:c r="H6" s="11"/>
-      <x:c r="I6" s="39"/>
-      <x:c r="J6" s="35"/>
-      <x:c r="K6" s="36"/>
-      <x:c r="L6" s="38"/>
-      <x:c r="M6" s="14"/>
-      <x:c r="N6" s="14"/>
-      <x:c r="O6" s="14"/>
-      <x:c r="P6" s="15"/>
-      <x:c r="Q6" s="13"/>
-      <x:c r="R6" s="14"/>
-      <x:c r="S6" s="9"/>
-      <x:c r="T6" s="13"/>
-      <x:c r="U6" s="14"/>
-      <x:c r="V6" s="9"/>
-      <x:c r="W6" s="13"/>
-      <x:c r="X6" s="14"/>
-      <x:c r="Y6" s="14"/>
-      <x:c r="Z6" s="32"/>
-      <x:c r="AA6" s="34"/>
-      <x:c r="AB6" s="34"/>
-      <x:c r="AC6" s="34"/>
-      <x:c r="AD6" s="34"/>
-      <x:c r="AE6" s="33"/>
+      <x:c r="H6" s="13"/>
+      <x:c r="I6" s="12"/>
+      <x:c r="J6" s="39"/>
+      <x:c r="K6" s="40"/>
+      <x:c r="L6" s="7"/>
+      <x:c r="M6" s="17"/>
+      <x:c r="N6" s="17"/>
+      <x:c r="O6" s="17"/>
+      <x:c r="P6" s="18"/>
+      <x:c r="Q6" s="16"/>
+      <x:c r="R6" s="17"/>
+      <x:c r="S6" s="10"/>
+      <x:c r="T6" s="16"/>
+      <x:c r="U6" s="17"/>
+      <x:c r="V6" s="10"/>
+      <x:c r="W6" s="16"/>
+      <x:c r="X6" s="17"/>
+      <x:c r="Y6" s="17"/>
+      <x:c r="Z6" s="37"/>
+      <x:c r="AA6" s="41"/>
+      <x:c r="AB6" s="41"/>
+      <x:c r="AC6" s="41"/>
+      <x:c r="AD6" s="41"/>
+      <x:c r="AE6" s="38"/>
     </x:row>
     <x:row r="7" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A7" s="32">
+      <x:c r="A7" s="37">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="33"/>
-      <x:c r="C7" s="16"/>
-      <x:c r="D7" s="17"/>
-      <x:c r="E7" s="17"/>
-      <x:c r="F7" s="11" t="str">
+      <x:c r="B7" s="38"/>
+      <x:c r="C7" s="19"/>
+      <x:c r="D7" s="20"/>
+      <x:c r="E7" s="20"/>
+      <x:c r="F7" s="13" t="str">
         <x:f>IF(LEN(G6)=0,"",H6)</x:f>
         <x:v/>
       </x:c>
-      <x:c r="G7" s="18" t="str">
+      <x:c r="G7" s="21" t="str">
         <x:f t="shared" ref="G7:G15" si="0">IF(OR(LEN(F7)=0,LEN(H7)=0),"",H7-F7)</x:f>
         <x:v/>
       </x:c>
-      <x:c r="H7" s="11"/>
-      <x:c r="I7" s="39"/>
-      <x:c r="J7" s="40"/>
-      <x:c r="K7" s="41"/>
-      <x:c r="L7" s="38"/>
-      <x:c r="M7" s="14"/>
-      <x:c r="N7" s="14"/>
-      <x:c r="O7" s="14"/>
-      <x:c r="P7" s="9"/>
-      <x:c r="Q7" s="13"/>
-      <x:c r="R7" s="14"/>
-      <x:c r="S7" s="9"/>
-      <x:c r="T7" s="13"/>
-      <x:c r="U7" s="14"/>
-      <x:c r="V7" s="9"/>
-      <x:c r="W7" s="13"/>
-      <x:c r="X7" s="14"/>
-      <x:c r="Y7" s="14"/>
-      <x:c r="Z7" s="32"/>
-      <x:c r="AA7" s="34"/>
-      <x:c r="AB7" s="34"/>
-      <x:c r="AC7" s="34"/>
-      <x:c r="AD7" s="34"/>
-      <x:c r="AE7" s="33"/>
+      <x:c r="H7" s="13"/>
+      <x:c r="I7" s="12"/>
+      <x:c r="J7" s="39"/>
+      <x:c r="K7" s="40"/>
+      <x:c r="L7" s="7"/>
+      <x:c r="M7" s="17"/>
+      <x:c r="N7" s="17"/>
+      <x:c r="O7" s="17"/>
+      <x:c r="P7" s="10"/>
+      <x:c r="Q7" s="16"/>
+      <x:c r="R7" s="17"/>
+      <x:c r="S7" s="10"/>
+      <x:c r="T7" s="16"/>
+      <x:c r="U7" s="17"/>
+      <x:c r="V7" s="10"/>
+      <x:c r="W7" s="16"/>
+      <x:c r="X7" s="17"/>
+      <x:c r="Y7" s="17"/>
+      <x:c r="Z7" s="37"/>
+      <x:c r="AA7" s="41"/>
+      <x:c r="AB7" s="41"/>
+      <x:c r="AC7" s="41"/>
+      <x:c r="AD7" s="41"/>
+      <x:c r="AE7" s="38"/>
     </x:row>
     <x:row r="8" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A8" s="32">
+      <x:c r="A8" s="37">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="33"/>
-      <x:c r="C8" s="16"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="17"/>
-      <x:c r="F8" s="11" t="str">
+      <x:c r="B8" s="38"/>
+      <x:c r="C8" s="19"/>
+      <x:c r="D8" s="20"/>
+      <x:c r="E8" s="20"/>
+      <x:c r="F8" s="13" t="str">
         <x:f t="shared" ref="F8:F15" si="1">IF(LEN(G7)=0,"",H7)</x:f>
         <x:v/>
       </x:c>
-      <x:c r="G8" s="12" t="str">
+      <x:c r="G8" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H8" s="11"/>
-      <x:c r="I8" s="37"/>
-      <x:c r="J8" s="40"/>
-      <x:c r="K8" s="41"/>
-      <x:c r="L8" s="38"/>
-      <x:c r="M8" s="14"/>
-      <x:c r="N8" s="14"/>
-      <x:c r="O8" s="14"/>
-      <x:c r="P8" s="9"/>
-      <x:c r="Q8" s="13"/>
-      <x:c r="R8" s="14"/>
-      <x:c r="S8" s="9"/>
-      <x:c r="T8" s="13"/>
-      <x:c r="U8" s="14"/>
-      <x:c r="V8" s="9"/>
-      <x:c r="W8" s="13"/>
-      <x:c r="X8" s="14"/>
-      <x:c r="Y8" s="14"/>
-      <x:c r="Z8" s="32"/>
-      <x:c r="AA8" s="34"/>
-      <x:c r="AB8" s="34"/>
-      <x:c r="AC8" s="34"/>
-      <x:c r="AD8" s="34"/>
-      <x:c r="AE8" s="33"/>
+      <x:c r="H8" s="13"/>
+      <x:c r="I8" s="15"/>
+      <x:c r="J8" s="39"/>
+      <x:c r="K8" s="40"/>
+      <x:c r="L8" s="7"/>
+      <x:c r="M8" s="17"/>
+      <x:c r="N8" s="17"/>
+      <x:c r="O8" s="17"/>
+      <x:c r="P8" s="10"/>
+      <x:c r="Q8" s="16"/>
+      <x:c r="R8" s="17"/>
+      <x:c r="S8" s="10"/>
+      <x:c r="T8" s="16"/>
+      <x:c r="U8" s="17"/>
+      <x:c r="V8" s="10"/>
+      <x:c r="W8" s="16"/>
+      <x:c r="X8" s="17"/>
+      <x:c r="Y8" s="17"/>
+      <x:c r="Z8" s="37"/>
+      <x:c r="AA8" s="41"/>
+      <x:c r="AB8" s="41"/>
+      <x:c r="AC8" s="41"/>
+      <x:c r="AD8" s="41"/>
+      <x:c r="AE8" s="38"/>
     </x:row>
     <x:row r="9" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A9" s="32">
+      <x:c r="A9" s="37">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="33"/>
-      <x:c r="C9" s="16"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="17"/>
-      <x:c r="F9" s="11" t="str">
+      <x:c r="B9" s="38"/>
+      <x:c r="C9" s="19"/>
+      <x:c r="D9" s="20"/>
+      <x:c r="E9" s="20"/>
+      <x:c r="F9" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G9" s="12" t="str">
+      <x:c r="G9" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H9" s="11"/>
-      <x:c r="I9" s="39"/>
-      <x:c r="J9" s="40"/>
-      <x:c r="K9" s="41"/>
-      <x:c r="L9" s="38"/>
-      <x:c r="M9" s="14"/>
-      <x:c r="N9" s="14"/>
-      <x:c r="O9" s="14"/>
-      <x:c r="P9" s="9"/>
-      <x:c r="Q9" s="13"/>
-      <x:c r="R9" s="14"/>
-      <x:c r="S9" s="9"/>
-      <x:c r="T9" s="13"/>
-      <x:c r="U9" s="14"/>
-      <x:c r="V9" s="9"/>
-      <x:c r="W9" s="13"/>
-      <x:c r="X9" s="14"/>
-      <x:c r="Y9" s="14"/>
-      <x:c r="Z9" s="32"/>
-      <x:c r="AA9" s="34"/>
-      <x:c r="AB9" s="34"/>
-      <x:c r="AC9" s="34"/>
-      <x:c r="AD9" s="34"/>
-      <x:c r="AE9" s="33"/>
+      <x:c r="H9" s="13"/>
+      <x:c r="I9" s="12"/>
+      <x:c r="J9" s="39"/>
+      <x:c r="K9" s="40"/>
+      <x:c r="L9" s="7"/>
+      <x:c r="M9" s="17"/>
+      <x:c r="N9" s="17"/>
+      <x:c r="O9" s="17"/>
+      <x:c r="P9" s="10"/>
+      <x:c r="Q9" s="16"/>
+      <x:c r="R9" s="17"/>
+      <x:c r="S9" s="10"/>
+      <x:c r="T9" s="16"/>
+      <x:c r="U9" s="17"/>
+      <x:c r="V9" s="10"/>
+      <x:c r="W9" s="16"/>
+      <x:c r="X9" s="17"/>
+      <x:c r="Y9" s="17"/>
+      <x:c r="Z9" s="37"/>
+      <x:c r="AA9" s="41"/>
+      <x:c r="AB9" s="41"/>
+      <x:c r="AC9" s="41"/>
+      <x:c r="AD9" s="41"/>
+      <x:c r="AE9" s="38"/>
     </x:row>
     <x:row r="10" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A10" s="32">
+      <x:c r="A10" s="37">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="33"/>
-      <x:c r="C10" s="16"/>
-      <x:c r="D10" s="17"/>
-      <x:c r="E10" s="17"/>
-      <x:c r="F10" s="11" t="str">
+      <x:c r="B10" s="38"/>
+      <x:c r="C10" s="19"/>
+      <x:c r="D10" s="20"/>
+      <x:c r="E10" s="20"/>
+      <x:c r="F10" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="G10" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H10" s="11"/>
-      <x:c r="I10" s="37"/>
-      <x:c r="J10" s="40"/>
-      <x:c r="K10" s="41"/>
-      <x:c r="L10" s="38"/>
-      <x:c r="M10" s="14"/>
-      <x:c r="N10" s="14"/>
-      <x:c r="O10" s="14"/>
-      <x:c r="P10" s="9"/>
-      <x:c r="Q10" s="13"/>
-      <x:c r="R10" s="14"/>
-      <x:c r="S10" s="9"/>
-      <x:c r="T10" s="13"/>
-      <x:c r="U10" s="14"/>
-      <x:c r="V10" s="9"/>
-      <x:c r="W10" s="13"/>
-      <x:c r="X10" s="14"/>
-      <x:c r="Y10" s="14"/>
-      <x:c r="Z10" s="32"/>
-      <x:c r="AA10" s="34"/>
-      <x:c r="AB10" s="34"/>
-      <x:c r="AC10" s="34"/>
-      <x:c r="AD10" s="34"/>
-      <x:c r="AE10" s="33"/>
+      <x:c r="H10" s="13"/>
+      <x:c r="I10" s="15"/>
+      <x:c r="J10" s="39"/>
+      <x:c r="K10" s="40"/>
+      <x:c r="L10" s="7"/>
+      <x:c r="M10" s="17"/>
+      <x:c r="N10" s="17"/>
+      <x:c r="O10" s="17"/>
+      <x:c r="P10" s="10"/>
+      <x:c r="Q10" s="16"/>
+      <x:c r="R10" s="17"/>
+      <x:c r="S10" s="10"/>
+      <x:c r="T10" s="16"/>
+      <x:c r="U10" s="17"/>
+      <x:c r="V10" s="10"/>
+      <x:c r="W10" s="16"/>
+      <x:c r="X10" s="17"/>
+      <x:c r="Y10" s="17"/>
+      <x:c r="Z10" s="37"/>
+      <x:c r="AA10" s="41"/>
+      <x:c r="AB10" s="41"/>
+      <x:c r="AC10" s="41"/>
+      <x:c r="AD10" s="41"/>
+      <x:c r="AE10" s="38"/>
     </x:row>
     <x:row r="11" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A11" s="32">
+      <x:c r="A11" s="37">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="33"/>
-      <x:c r="C11" s="16"/>
-      <x:c r="D11" s="17"/>
-      <x:c r="E11" s="17"/>
-      <x:c r="F11" s="11" t="str">
+      <x:c r="B11" s="38"/>
+      <x:c r="C11" s="19"/>
+      <x:c r="D11" s="20"/>
+      <x:c r="E11" s="20"/>
+      <x:c r="F11" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G11" s="12" t="str">
+      <x:c r="G11" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H11" s="11"/>
-      <x:c r="I11" s="37"/>
-      <x:c r="J11" s="40"/>
-      <x:c r="K11" s="41"/>
-      <x:c r="L11" s="38"/>
-      <x:c r="M11" s="7"/>
-      <x:c r="N11" s="14"/>
-      <x:c r="O11" s="14"/>
-      <x:c r="P11" s="9"/>
-      <x:c r="Q11" s="13"/>
-      <x:c r="R11" s="14"/>
-      <x:c r="S11" s="9"/>
-      <x:c r="T11" s="13"/>
-      <x:c r="U11" s="14"/>
-      <x:c r="V11" s="9"/>
-      <x:c r="W11" s="8"/>
-      <x:c r="X11" s="7"/>
-      <x:c r="Y11" s="7"/>
-      <x:c r="Z11" s="32"/>
-      <x:c r="AA11" s="34"/>
-      <x:c r="AB11" s="34"/>
-      <x:c r="AC11" s="34"/>
-      <x:c r="AD11" s="34"/>
-      <x:c r="AE11" s="33"/>
+      <x:c r="H11" s="13"/>
+      <x:c r="I11" s="15"/>
+      <x:c r="J11" s="42"/>
+      <x:c r="K11" s="42"/>
+      <x:c r="L11" s="7"/>
+      <x:c r="M11" s="8"/>
+      <x:c r="N11" s="17"/>
+      <x:c r="O11" s="17"/>
+      <x:c r="P11" s="10"/>
+      <x:c r="Q11" s="16"/>
+      <x:c r="R11" s="17"/>
+      <x:c r="S11" s="10"/>
+      <x:c r="T11" s="16"/>
+      <x:c r="U11" s="17"/>
+      <x:c r="V11" s="10"/>
+      <x:c r="W11" s="9"/>
+      <x:c r="X11" s="8"/>
+      <x:c r="Y11" s="8"/>
+      <x:c r="Z11" s="37"/>
+      <x:c r="AA11" s="41"/>
+      <x:c r="AB11" s="41"/>
+      <x:c r="AC11" s="41"/>
+      <x:c r="AD11" s="41"/>
+      <x:c r="AE11" s="38"/>
     </x:row>
     <x:row r="12" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A12" s="32">
+      <x:c r="A12" s="37">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="33"/>
-      <x:c r="C12" s="16"/>
-      <x:c r="D12" s="17"/>
-      <x:c r="E12" s="17"/>
-      <x:c r="F12" s="11" t="str">
+      <x:c r="B12" s="38"/>
+      <x:c r="C12" s="19"/>
+      <x:c r="D12" s="20"/>
+      <x:c r="E12" s="20"/>
+      <x:c r="F12" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="G12" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H12" s="11"/>
-      <x:c r="I12" s="37"/>
-      <x:c r="J12" s="40"/>
-      <x:c r="K12" s="41"/>
-      <x:c r="L12" s="38"/>
-      <x:c r="M12" s="7"/>
-      <x:c r="N12" s="14"/>
-      <x:c r="O12" s="14"/>
-      <x:c r="P12" s="9"/>
-      <x:c r="Q12" s="13"/>
-      <x:c r="R12" s="14"/>
-      <x:c r="S12" s="9"/>
-      <x:c r="T12" s="13"/>
-      <x:c r="U12" s="14"/>
-      <x:c r="V12" s="9"/>
-      <x:c r="W12" s="8"/>
-      <x:c r="X12" s="7"/>
-      <x:c r="Y12" s="7"/>
-      <x:c r="Z12" s="32"/>
-      <x:c r="AA12" s="34"/>
-      <x:c r="AB12" s="34"/>
-      <x:c r="AC12" s="34"/>
-      <x:c r="AD12" s="34"/>
-      <x:c r="AE12" s="33"/>
+      <x:c r="H12" s="13"/>
+      <x:c r="I12" s="15"/>
+      <x:c r="J12" s="42"/>
+      <x:c r="K12" s="42"/>
+      <x:c r="L12" s="7"/>
+      <x:c r="M12" s="8"/>
+      <x:c r="N12" s="17"/>
+      <x:c r="O12" s="17"/>
+      <x:c r="P12" s="10"/>
+      <x:c r="Q12" s="16"/>
+      <x:c r="R12" s="17"/>
+      <x:c r="S12" s="10"/>
+      <x:c r="T12" s="16"/>
+      <x:c r="U12" s="17"/>
+      <x:c r="V12" s="10"/>
+      <x:c r="W12" s="9"/>
+      <x:c r="X12" s="8"/>
+      <x:c r="Y12" s="8"/>
+      <x:c r="Z12" s="37"/>
+      <x:c r="AA12" s="41"/>
+      <x:c r="AB12" s="41"/>
+      <x:c r="AC12" s="41"/>
+      <x:c r="AD12" s="41"/>
+      <x:c r="AE12" s="38"/>
       <x:c r="AF12" s="1"/>
       <x:c r="AG12" s="1"/>
       <x:c r="AH12" s="1"/>
@@ -1669,45 +1679,45 @@
       <x:c r="AN12" s="1"/>
     </x:row>
     <x:row r="13" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A13" s="32">
+      <x:c r="A13" s="37">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="33"/>
-      <x:c r="C13" s="16"/>
-      <x:c r="D13" s="17"/>
-      <x:c r="E13" s="17"/>
-      <x:c r="F13" s="11" t="str">
+      <x:c r="B13" s="38"/>
+      <x:c r="C13" s="19"/>
+      <x:c r="D13" s="20"/>
+      <x:c r="E13" s="20"/>
+      <x:c r="F13" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G13" s="12" t="str">
+      <x:c r="G13" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H13" s="11"/>
-      <x:c r="I13" s="37"/>
-      <x:c r="J13" s="40"/>
-      <x:c r="K13" s="41"/>
-      <x:c r="L13" s="38"/>
-      <x:c r="M13" s="7"/>
-      <x:c r="N13" s="14"/>
-      <x:c r="O13" s="14"/>
-      <x:c r="P13" s="9"/>
-      <x:c r="Q13" s="13"/>
-      <x:c r="R13" s="14"/>
-      <x:c r="S13" s="9"/>
-      <x:c r="T13" s="13"/>
-      <x:c r="U13" s="14"/>
-      <x:c r="V13" s="9"/>
-      <x:c r="W13" s="8"/>
-      <x:c r="X13" s="7"/>
-      <x:c r="Y13" s="7"/>
-      <x:c r="Z13" s="32"/>
-      <x:c r="AA13" s="34"/>
-      <x:c r="AB13" s="34"/>
-      <x:c r="AC13" s="34"/>
-      <x:c r="AD13" s="34"/>
-      <x:c r="AE13" s="33"/>
+      <x:c r="H13" s="13"/>
+      <x:c r="I13" s="15"/>
+      <x:c r="J13" s="42"/>
+      <x:c r="K13" s="42"/>
+      <x:c r="L13" s="7"/>
+      <x:c r="M13" s="8"/>
+      <x:c r="N13" s="17"/>
+      <x:c r="O13" s="17"/>
+      <x:c r="P13" s="10"/>
+      <x:c r="Q13" s="16"/>
+      <x:c r="R13" s="17"/>
+      <x:c r="S13" s="10"/>
+      <x:c r="T13" s="16"/>
+      <x:c r="U13" s="17"/>
+      <x:c r="V13" s="10"/>
+      <x:c r="W13" s="9"/>
+      <x:c r="X13" s="8"/>
+      <x:c r="Y13" s="8"/>
+      <x:c r="Z13" s="37"/>
+      <x:c r="AA13" s="41"/>
+      <x:c r="AB13" s="41"/>
+      <x:c r="AC13" s="41"/>
+      <x:c r="AD13" s="41"/>
+      <x:c r="AE13" s="38"/>
       <x:c r="AF13" s="1"/>
       <x:c r="AG13" s="1"/>
       <x:c r="AH13" s="1"/>
@@ -1719,45 +1729,45 @@
       <x:c r="AN13" s="1"/>
     </x:row>
     <x:row r="14" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A14" s="32">
+      <x:c r="A14" s="37">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="33"/>
-      <x:c r="C14" s="16"/>
-      <x:c r="D14" s="17"/>
-      <x:c r="E14" s="17"/>
-      <x:c r="F14" s="11" t="str">
+      <x:c r="B14" s="38"/>
+      <x:c r="C14" s="19"/>
+      <x:c r="D14" s="20"/>
+      <x:c r="E14" s="20"/>
+      <x:c r="F14" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G14" s="12" t="str">
+      <x:c r="G14" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H14" s="11"/>
-      <x:c r="I14" s="37"/>
-      <x:c r="J14" s="40"/>
-      <x:c r="K14" s="41"/>
-      <x:c r="L14" s="38"/>
-      <x:c r="M14" s="7"/>
-      <x:c r="N14" s="14"/>
-      <x:c r="O14" s="14"/>
-      <x:c r="P14" s="9"/>
-      <x:c r="Q14" s="13"/>
-      <x:c r="R14" s="14"/>
-      <x:c r="S14" s="9"/>
-      <x:c r="T14" s="13"/>
-      <x:c r="U14" s="7"/>
-      <x:c r="V14" s="9"/>
-      <x:c r="W14" s="8"/>
-      <x:c r="X14" s="7"/>
-      <x:c r="Y14" s="7"/>
-      <x:c r="Z14" s="32"/>
-      <x:c r="AA14" s="34"/>
-      <x:c r="AB14" s="34"/>
-      <x:c r="AC14" s="34"/>
-      <x:c r="AD14" s="34"/>
-      <x:c r="AE14" s="33"/>
+      <x:c r="H14" s="13"/>
+      <x:c r="I14" s="15"/>
+      <x:c r="J14" s="42"/>
+      <x:c r="K14" s="42"/>
+      <x:c r="L14" s="7"/>
+      <x:c r="M14" s="8"/>
+      <x:c r="N14" s="17"/>
+      <x:c r="O14" s="17"/>
+      <x:c r="P14" s="10"/>
+      <x:c r="Q14" s="16"/>
+      <x:c r="R14" s="17"/>
+      <x:c r="S14" s="10"/>
+      <x:c r="T14" s="16"/>
+      <x:c r="U14" s="8"/>
+      <x:c r="V14" s="10"/>
+      <x:c r="W14" s="9"/>
+      <x:c r="X14" s="8"/>
+      <x:c r="Y14" s="8"/>
+      <x:c r="Z14" s="37"/>
+      <x:c r="AA14" s="41"/>
+      <x:c r="AB14" s="41"/>
+      <x:c r="AC14" s="41"/>
+      <x:c r="AD14" s="41"/>
+      <x:c r="AE14" s="38"/>
       <x:c r="AF14" s="1"/>
       <x:c r="AG14" s="1"/>
       <x:c r="AH14" s="1"/>
@@ -1769,45 +1779,45 @@
       <x:c r="AN14" s="1"/>
     </x:row>
     <x:row r="15" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A15" s="32">
+      <x:c r="A15" s="37">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B15" s="33"/>
-      <x:c r="C15" s="16"/>
-      <x:c r="D15" s="17"/>
-      <x:c r="E15" s="17"/>
-      <x:c r="F15" s="11" t="str">
+      <x:c r="B15" s="38"/>
+      <x:c r="C15" s="19"/>
+      <x:c r="D15" s="20"/>
+      <x:c r="E15" s="20"/>
+      <x:c r="F15" s="13" t="str">
         <x:f t="shared" si="1"/>
         <x:v/>
       </x:c>
-      <x:c r="G15" s="12" t="str">
+      <x:c r="G15" s="14" t="str">
         <x:f t="shared" si="0"/>
         <x:v/>
       </x:c>
-      <x:c r="H15" s="11"/>
-      <x:c r="I15" s="39"/>
+      <x:c r="H15" s="13"/>
+      <x:c r="I15" s="12"/>
       <x:c r="J15" s="42"/>
-      <x:c r="K15" s="43"/>
-      <x:c r="L15" s="38"/>
-      <x:c r="M15" s="7"/>
-      <x:c r="N15" s="14"/>
-      <x:c r="O15" s="14"/>
-      <x:c r="P15" s="9"/>
-      <x:c r="Q15" s="13"/>
-      <x:c r="R15" s="14"/>
-      <x:c r="S15" s="9"/>
-      <x:c r="T15" s="13"/>
-      <x:c r="U15" s="7"/>
-      <x:c r="V15" s="9"/>
-      <x:c r="W15" s="8"/>
-      <x:c r="X15" s="7"/>
-      <x:c r="Y15" s="7"/>
-      <x:c r="Z15" s="32"/>
-      <x:c r="AA15" s="34"/>
-      <x:c r="AB15" s="34"/>
-      <x:c r="AC15" s="34"/>
-      <x:c r="AD15" s="34"/>
-      <x:c r="AE15" s="33"/>
+      <x:c r="K15" s="42"/>
+      <x:c r="L15" s="7"/>
+      <x:c r="M15" s="8"/>
+      <x:c r="N15" s="17"/>
+      <x:c r="O15" s="17"/>
+      <x:c r="P15" s="10"/>
+      <x:c r="Q15" s="16"/>
+      <x:c r="R15" s="17"/>
+      <x:c r="S15" s="10"/>
+      <x:c r="T15" s="16"/>
+      <x:c r="U15" s="8"/>
+      <x:c r="V15" s="10"/>
+      <x:c r="W15" s="9"/>
+      <x:c r="X15" s="8"/>
+      <x:c r="Y15" s="8"/>
+      <x:c r="Z15" s="37"/>
+      <x:c r="AA15" s="41"/>
+      <x:c r="AB15" s="41"/>
+      <x:c r="AC15" s="41"/>
+      <x:c r="AD15" s="41"/>
+      <x:c r="AE15" s="38"/>
       <x:c r="AF15" s="1"/>
       <x:c r="AG15" s="1"/>
       <x:c r="AH15" s="1"/>
@@ -1985,7 +1995,7 @@
       <x:c r="AN30" s="1"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="32">
+  <x:mergeCells count="42">
     <x:mergeCell ref="C1:J2"/>
     <x:mergeCell ref="N1:S1"/>
     <x:mergeCell ref="T1:Y1"/>
@@ -1999,24 +2009,34 @@
     <x:mergeCell ref="N5:Y5"/>
     <x:mergeCell ref="Z5:AE5"/>
     <x:mergeCell ref="A6:B6"/>
+    <x:mergeCell ref="J6:K6"/>
     <x:mergeCell ref="Z6:AE6"/>
     <x:mergeCell ref="A7:B7"/>
+    <x:mergeCell ref="J7:K7"/>
     <x:mergeCell ref="Z7:AE7"/>
     <x:mergeCell ref="A8:B8"/>
+    <x:mergeCell ref="J8:K8"/>
     <x:mergeCell ref="Z8:AE8"/>
     <x:mergeCell ref="A9:B9"/>
+    <x:mergeCell ref="J9:K9"/>
     <x:mergeCell ref="Z9:AE9"/>
     <x:mergeCell ref="A10:B10"/>
+    <x:mergeCell ref="J10:K10"/>
     <x:mergeCell ref="Z10:AE10"/>
     <x:mergeCell ref="A11:B11"/>
+    <x:mergeCell ref="J11:K11"/>
     <x:mergeCell ref="Z11:AE11"/>
     <x:mergeCell ref="A12:B12"/>
+    <x:mergeCell ref="J12:K12"/>
     <x:mergeCell ref="Z12:AE12"/>
     <x:mergeCell ref="A13:B13"/>
+    <x:mergeCell ref="J13:K13"/>
     <x:mergeCell ref="Z13:AE13"/>
     <x:mergeCell ref="A14:B14"/>
+    <x:mergeCell ref="J14:K14"/>
     <x:mergeCell ref="Z14:AE14"/>
     <x:mergeCell ref="A15:B15"/>
+    <x:mergeCell ref="J15:K15"/>
     <x:mergeCell ref="Z15:AE15"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="1" verticalCentered="1" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/car_log_template.xlsx
+++ b/car_log_template.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\복구\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -109,19 +109,8 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>도착시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출발시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운행목적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주유(원)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주유량(L)</x:t>
+    <x:t>잔여유류량
+(Empty⇔Full)</x:t>
   </x:si>
   <x:si>
     <x:t>운행 전
@@ -139,10 +128,6 @@
     <x:t>사용자   서명</x:t>
   </x:si>
   <x:si>
-    <x:t>잔여유류량
-(Empty⇔Full)</x:t>
-  </x:si>
-  <x:si>
     <x:t>담당</x:t>
   </x:si>
   <x:si>
@@ -152,10 +137,25 @@
     <x:t xml:space="preserve">날짜 </x:t>
   </x:si>
   <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
     <x:t>대리</x:t>
   </x:si>
   <x:si>
-    <x:t>구분</x:t>
+    <x:t>도착시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출발시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운행목적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주유(원)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주유량(L)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1230,7 +1230,7 @@
       <x:c r="I1" s="22"/>
       <x:c r="J1" s="22"/>
       <x:c r="N1" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="O1" s="24"/>
       <x:c r="P1" s="23"/>
@@ -1238,7 +1238,7 @@
       <x:c r="R1" s="23"/>
       <x:c r="S1" s="23"/>
       <x:c r="T1" s="23" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="U1" s="23"/>
       <x:c r="V1" s="23"/>
@@ -1327,42 +1327,42 @@
     </x:row>
     <x:row r="5" spans="1:32" ht="34" customHeight="1">
       <x:c r="A5" s="29" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="30"/>
       <x:c r="C5" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J5" s="31" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K5" s="32"/>
       <x:c r="L5" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="N5" s="33" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O5" s="34"/>
       <x:c r="P5" s="35"/>
@@ -1376,7 +1376,7 @@
       <x:c r="X5" s="34"/>
       <x:c r="Y5" s="34"/>
       <x:c r="Z5" s="33" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AA5" s="34"/>
       <x:c r="AB5" s="34"/>
@@ -1386,9 +1386,7 @@
       <x:c r="AF5" s="11"/>
     </x:row>
     <x:row r="6" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A6" s="37">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A6" s="37"/>
       <x:c r="B6" s="38"/>
       <x:c r="C6" s="19"/>
       <x:c r="D6" s="20"/>
@@ -1424,9 +1422,7 @@
       <x:c r="AE6" s="38"/>
     </x:row>
     <x:row r="7" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A7" s="37">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A7" s="37"/>
       <x:c r="B7" s="38"/>
       <x:c r="C7" s="19"/>
       <x:c r="D7" s="20"/>
@@ -1465,9 +1461,7 @@
       <x:c r="AE7" s="38"/>
     </x:row>
     <x:row r="8" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A8" s="37">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A8" s="37"/>
       <x:c r="B8" s="38"/>
       <x:c r="C8" s="19"/>
       <x:c r="D8" s="20"/>
@@ -1506,9 +1500,7 @@
       <x:c r="AE8" s="38"/>
     </x:row>
     <x:row r="9" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A9" s="37">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="A9" s="37"/>
       <x:c r="B9" s="38"/>
       <x:c r="C9" s="19"/>
       <x:c r="D9" s="20"/>
@@ -1547,9 +1539,7 @@
       <x:c r="AE9" s="38"/>
     </x:row>
     <x:row r="10" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A10" s="37">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A10" s="37"/>
       <x:c r="B10" s="38"/>
       <x:c r="C10" s="19"/>
       <x:c r="D10" s="20"/>
@@ -1588,9 +1578,7 @@
       <x:c r="AE10" s="38"/>
     </x:row>
     <x:row r="11" spans="1:31" ht="33.5" customHeight="1">
-      <x:c r="A11" s="37">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A11" s="37"/>
       <x:c r="B11" s="38"/>
       <x:c r="C11" s="19"/>
       <x:c r="D11" s="20"/>
@@ -1629,9 +1617,7 @@
       <x:c r="AE11" s="38"/>
     </x:row>
     <x:row r="12" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A12" s="37">
-        <x:v>7</x:v>
-      </x:c>
+      <x:c r="A12" s="37"/>
       <x:c r="B12" s="38"/>
       <x:c r="C12" s="19"/>
       <x:c r="D12" s="20"/>
@@ -1679,9 +1665,7 @@
       <x:c r="AN12" s="1"/>
     </x:row>
     <x:row r="13" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A13" s="37">
-        <x:v>8</x:v>
-      </x:c>
+      <x:c r="A13" s="37"/>
       <x:c r="B13" s="38"/>
       <x:c r="C13" s="19"/>
       <x:c r="D13" s="20"/>
@@ -1729,9 +1713,7 @@
       <x:c r="AN13" s="1"/>
     </x:row>
     <x:row r="14" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A14" s="37">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="A14" s="37"/>
       <x:c r="B14" s="38"/>
       <x:c r="C14" s="19"/>
       <x:c r="D14" s="20"/>
@@ -1779,9 +1761,7 @@
       <x:c r="AN14" s="1"/>
     </x:row>
     <x:row r="15" spans="1:40" ht="33.5" customHeight="1">
-      <x:c r="A15" s="37">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="A15" s="37"/>
       <x:c r="B15" s="38"/>
       <x:c r="C15" s="19"/>
       <x:c r="D15" s="20"/>
